--- a/fixtures/fluorocycler-xt/results.xlsx
+++ b/fixtures/fluorocycler-xt/results.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -17,7 +22,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -45,9 +50,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -194,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -229,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -264,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -395,46 +402,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -445,299 +413,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SampleID</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>WellPosition</t>
+          <t>Col</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>AssayName</t>
+          <t>Sample ID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TargetName</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>TargetNo</t>
+          <t>Calc. Conc.</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>CalcConc</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>CalcConcUnit</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>RunDate</t>
+          <t>Result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>DEV01263000000000001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HIV-1 VL</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VIH-1</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>1250</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Positive</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>copies/mL</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>DEV01263000000000001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HIV-1 VL</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Valid</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>DEV01263000000000002</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HIV-1 VL</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VIH-1</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="G4" t="inlineStr">
+        <v>450</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Positive</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>450</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>copies/mL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>DEV01263000000000002</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HIV-1 VL</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Valid</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DEV01263000000000003</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HIV-1 VL</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VIH-1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DEV01263000000000003</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>HIV-1 VL</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
         </is>
       </c>
     </row>
